--- a/examples/acme-corp/equipment_register.xlsx
+++ b/examples/acme-corp/equipment_register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="1" r:id="Rdb7a473536644017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" r:id="R74d4c144d5a6475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оборудование" sheetId="1" r:id="R19dd2d1feb7c44fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" r:id="R3c0c14de2ee2411b"/>
   </x:sheets>
 </x:workbook>
 </file>
